--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsThirdChannelRefTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsThirdChannelRefTemplate.xlsx
@@ -32,6 +32,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -46,6 +53,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -60,6 +74,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -74,6 +95,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -93,21 +121,17 @@
     <t>物流商编码</t>
   </si>
   <si>
-    <r>
-      <t>*</t>
-    </r>
+    <t>查询渠道名称</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>查询渠道名称</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>*</t>
     </r>
     <r>
@@ -122,6 +146,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1136,7 +1167,7 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsThirdChannelRefTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsThirdChannelRefTemplate.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <r>
       <rPr>
@@ -49,6 +49,20 @@
         <scheme val="minor"/>
       </rPr>
       <t>序号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>平台</t>
     </r>
   </si>
   <si>
@@ -1135,20 +1149,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.625" customWidth="1"/>
-    <col min="2" max="2" width="18.375" customWidth="1"/>
-    <col min="3" max="4" width="16.375" customWidth="1"/>
-    <col min="5" max="6" width="18.5" customWidth="1"/>
-    <col min="7" max="8" width="17.625" customWidth="1"/>
-    <col min="9" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="15.625" customWidth="1"/>
-    <col min="12" max="12" width="19.625" customWidth="1"/>
+    <col min="1" max="2" width="11.625" customWidth="1"/>
+    <col min="3" max="3" width="18.375" customWidth="1"/>
+    <col min="4" max="5" width="16.375" customWidth="1"/>
+    <col min="6" max="7" width="18.5" customWidth="1"/>
+    <col min="8" max="9" width="17.625" customWidth="1"/>
+    <col min="10" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="15.625" customWidth="1"/>
+    <col min="13" max="13" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1161,40 +1175,43 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
       <formula1>"track123"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I$1:I$1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I$1:I$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"按照默认发件人,按照默认收件人,按照默认订单收件人,按照默认发件人-店铺,按照默认发件人-平台"</formula1>
     </dataValidation>
   </dataValidations>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsThirdChannelRefTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsThirdChannelRefTemplate.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <r>
       <rPr>
@@ -53,6 +53,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -129,13 +136,7 @@
     </r>
   </si>
   <si>
-    <t>查询物流商</t>
-  </si>
-  <si>
-    <t>物流商编码</t>
-  </si>
-  <si>
-    <t>查询渠道名称</t>
+    <t>查询物流商（中文）</t>
   </si>
   <si>
     <r>
@@ -822,14 +823,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1149,20 +1147,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="11.625" customWidth="1"/>
     <col min="3" max="3" width="18.375" customWidth="1"/>
     <col min="4" max="5" width="16.375" customWidth="1"/>
-    <col min="6" max="7" width="18.5" customWidth="1"/>
-    <col min="8" max="9" width="17.625" customWidth="1"/>
-    <col min="10" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="15.625" customWidth="1"/>
-    <col min="13" max="13" width="19.625" customWidth="1"/>
+    <col min="6" max="6" width="18.5" customWidth="1"/>
+    <col min="7" max="7" width="17.625" customWidth="1"/>
+    <col min="8" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="15.625" customWidth="1"/>
+    <col min="11" max="11" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1181,37 +1179,31 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
-      <formula1>"track123"</formula1>
+      <formula1>"track123,快递100"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I$1:I$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576">
       <formula1>"按照默认发件人,按照默认收件人,按照默认订单收件人,按照默认发件人-店铺,按照默认发件人-平台"</formula1>
     </dataValidation>
   </dataValidations>

--- a/erp-server/erp-server-tms/src/main/resources/excel/logisticsThirdChannelRefTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/logisticsThirdChannelRefTemplate.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <r>
       <rPr>
@@ -160,34 +160,13 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="9"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>推送类型</t>
-    </r>
+    <t>推送类型</t>
   </si>
   <si>
-    <t>默认手机号</t>
+    <t>店铺名称</t>
   </si>
   <si>
-    <t>店铺/平台名称</t>
-  </si>
-  <si>
-    <t>店铺/平台手机号码</t>
+    <t>店铺手机号码</t>
   </si>
 </sst>
 </file>
@@ -200,7 +179,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,13 +196,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -693,137 +665,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -831,9 +803,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1147,7 +1116,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="11.625" customWidth="1"/>
@@ -1155,12 +1124,12 @@
     <col min="4" max="5" width="16.375" customWidth="1"/>
     <col min="6" max="6" width="18.5" customWidth="1"/>
     <col min="7" max="7" width="17.625" customWidth="1"/>
-    <col min="8" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="15.625" customWidth="1"/>
-    <col min="11" max="11" width="19.625" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="15.625" customWidth="1"/>
+    <col min="10" max="10" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1176,35 +1145,33 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
       <formula1>"track123,快递100"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576">
-      <formula1>"按照默认发件人,按照默认收件人,按照默认订单收件人,按照默认发件人-店铺,按照默认发件人-平台"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
+      <formula1>"按照默认发件人,按照默认收件人,按照默认订单收件人,按照默认发件人-店铺"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
